--- a/optimized_version/metadata/validation_daily_metrics/agus7_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus7_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09696351143912785</v>
+        <v>0.1207572613247764</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0350894464101259</v>
+        <v>0.04369999999999408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0350894464101259</v>
+        <v>0.04369999999999408</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>8.37010472503874</v>
+        <v>8.371061703095558</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -503,10 +503,10 @@
         <v>2.802354166666666</v>
       </c>
       <c r="F3" t="n">
-        <v>4.142912296527375</v>
+        <v>4.143963666135358</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4738425529677101</v>
+        <v>0.4735754673517265</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>4.84018137669365</v>
+        <v>4.836187301486302</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1.696439258931646</v>
+        <v>1.695245833333334</v>
       </c>
       <c r="F4" t="n">
-        <v>3.753392828328369</v>
+        <v>3.752317210682399</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4782993867646693</v>
+        <v>0.478598353596094</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>3.553229252136905</v>
+        <v>3.552165285163458</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.343642546132489</v>
+        <v>1.342925</v>
       </c>
       <c r="F5" t="n">
-        <v>1.706345353439241</v>
+        <v>1.704690086447778</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8060249854954329</v>
+        <v>0.8064011399514824</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>4.253366907900861</v>
+        <v>4.257370549256783</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.641039907735021</v>
+        <v>1.642474999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.968888402137255</v>
+        <v>1.969613594930063</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01416859609309751</v>
+        <v>-0.01491582300725858</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>2.873808716473094</v>
+        <v>2.872184556420647</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16228004613249</v>
+        <v>1.1615625</v>
       </c>
       <c r="F7" t="n">
-        <v>1.692117359870177</v>
+        <v>1.692755898798366</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4819409935210113</v>
+        <v>0.4815499293238886</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>4.811211389625075</v>
+        <v>4.811986362172668</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -633,10 +633,10 @@
         <v>1.373749999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>3.381575125624729</v>
+        <v>3.382874077214766</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5366767931080845</v>
+        <v>0.5363207755812733</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>6.370782440017229</v>
+        <v>6.373306133239377</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.366074120534177</v>
+        <v>2.366791666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>4.348840313733715</v>
+        <v>4.347787197145999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2499528201200522</v>
+        <v>0.2503160394751272</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>3.475598179003122</v>
+        <v>3.475864490707604</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -685,10 +685,10 @@
         <v>1.391091666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>1.685253904385493</v>
+        <v>1.685186773278658</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4374338424802833</v>
+        <v>-0.4373193260828969</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>1.890856155391772</v>
+        <v>1.889550496156966</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7311258794658212</v>
+        <v>0.7304416666666654</v>
       </c>
       <c r="F11" t="n">
-        <v>1.131633439061968</v>
+        <v>1.130770086692397</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6214338845659095</v>
+        <v>0.6220112999474778</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>4.456079992201011</v>
+        <v>4.456592836555367</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.707887500000002</v>
+        <v>1.707887500000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.168689935841066</v>
+        <v>2.168808444457464</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3173982654583116</v>
+        <v>0.3173236615271402</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>2.32233061293296</v>
+        <v>2.326049509136324</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9456690744016877</v>
+        <v>0.9471041666666657</v>
       </c>
       <c r="F13" t="n">
-        <v>1.155822278093958</v>
+        <v>1.15621579643104</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08396389308273267</v>
+        <v>0.08334002836332033</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>5.251433211768191</v>
+        <v>5.250331574655192</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.902630046132489</v>
+        <v>1.901912500000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.643586260921925</v>
+        <v>2.643826298268604</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3681974473247694</v>
+        <v>0.3680827069088464</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>4.694221179535313</v>
+        <v>4.694954507823409</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -815,10 +815,10 @@
         <v>1.838116666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>2.440223801885707</v>
+        <v>2.440407160231328</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2140842153531709</v>
+        <v>0.2139661035374</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>9.667332338067597</v>
+        <v>9.660550471814894</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3.07334101786329</v>
+        <v>3.070470833333333</v>
       </c>
       <c r="F16" t="n">
-        <v>4.680317319701484</v>
+        <v>4.679753327589321</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4744454290169755</v>
+        <v>0.4745720831531123</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>2.098741051135931</v>
+        <v>2.103130130865802</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8643940744016883</v>
+        <v>0.8662041666666657</v>
       </c>
       <c r="F17" t="n">
-        <v>1.352830018988256</v>
+        <v>1.353071005928119</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5603101749994412</v>
+        <v>0.5601535123862541</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>3.567882390618344</v>
+        <v>3.56807724525173</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -893,10 +893,10 @@
         <v>1.407020833333332</v>
       </c>
       <c r="F18" t="n">
-        <v>1.813520469677177</v>
+        <v>1.813717415627362</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1329254117030226</v>
+        <v>0.1327370751454201</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>3.636871162529902</v>
+        <v>3.634615217134221</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.277946712799156</v>
+        <v>1.277229166666667</v>
       </c>
       <c r="F19" t="n">
-        <v>2.323464020966402</v>
+        <v>2.324063000347308</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3551277803815112</v>
+        <v>0.3547952467608811</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>5.503595585921515</v>
+        <v>5.503993974654811</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -945,10 +945,10 @@
         <v>1.912220833333333</v>
       </c>
       <c r="F20" t="n">
-        <v>2.362949879254615</v>
+        <v>2.363775275821145</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07193456742385418</v>
+        <v>0.07128609339824576</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>4.380415998588433</v>
+        <v>4.379212350479129</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.567434212799156</v>
+        <v>1.566716666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>1.93380111987232</v>
+        <v>1.932379545405095</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6761483363339023</v>
+        <v>0.6766243005214039</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>4.482193790846301</v>
+        <v>4.476351758575616</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.611890138397469</v>
+        <v>1.609737500000002</v>
       </c>
       <c r="F22" t="n">
-        <v>2.24629202940471</v>
+        <v>2.24547884991524</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8135902057557826</v>
+        <v>0.8137251456316139</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>10.73973054659049</v>
+        <v>10.74083882593703</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1023,10 +1023,10 @@
         <v>3.588416666666668</v>
       </c>
       <c r="F23" t="n">
-        <v>5.237687387799955</v>
+        <v>5.238760624979284</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.03709532028939799</v>
+        <v>-0.03752037936965325</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>3.501319456377972</v>
+        <v>3.495126510781912</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.261448471730801</v>
+        <v>1.259295833333334</v>
       </c>
       <c r="F24" t="n">
-        <v>1.780436755541178</v>
+        <v>1.777967324760686</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7773470697012936</v>
+        <v>0.7779642718555515</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>4.087076401786809</v>
+        <v>4.091701733662049</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.404527407735022</v>
+        <v>1.4059625</v>
       </c>
       <c r="F25" t="n">
-        <v>2.043085235329979</v>
+        <v>2.044268245505793</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5222736929944312</v>
+        <v>0.521720295912518</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>3.702823402223954</v>
+        <v>3.705588242921249</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.176749120534177</v>
+        <v>1.177466666666666</v>
       </c>
       <c r="F26" t="n">
-        <v>1.650907939144748</v>
+        <v>1.651794116508873</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5772549254307917</v>
+        <v>0.576800959884312</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>2.082547384834148</v>
+        <v>2.089687992527154</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6501306949358646</v>
+        <v>0.6522833333333314</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8797547878168175</v>
+        <v>0.8798919128696041</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.696032551455783</v>
+        <v>-1.696873063886372</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>3.905378642940509</v>
+        <v>3.903433095380862</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.22085504613249</v>
+        <v>1.2201375</v>
       </c>
       <c r="F28" t="n">
-        <v>1.708402841272792</v>
+        <v>1.708874525699103</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2655079763367695</v>
+        <v>0.2651023386650432</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>6.021950318522104</v>
+        <v>6.017839927674535</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.621418425598312</v>
+        <v>1.619983333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>3.035468547264865</v>
+        <v>3.0354598332323</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4133079326826224</v>
+        <v>0.413311301155306</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>4.754750573701014</v>
+        <v>4.755576891173575</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.472556833333332</v>
+        <v>1.472556833367287</v>
       </c>
       <c r="F30" t="n">
-        <v>1.837208782788207</v>
+        <v>1.836866873308329</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.09726396554426908</v>
+        <v>-0.09685559601581861</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.4916565119852666</v>
+        <v>0.4660264521304893</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.165174553689915</v>
+        <v>0.1565640021342833</v>
       </c>
       <c r="F31" t="n">
-        <v>0.165174553689915</v>
+        <v>0.1565640021342834</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9791530192588473</v>
+        <v>0.9812698735272054</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>1.897719410767415</v>
+        <v>1.899998752093389</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6606699538675102</v>
+        <v>0.6613874999999991</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8073141101087211</v>
+        <v>0.806997621072495</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3960030542283201</v>
+        <v>0.3964765277851815</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>3.254299194411435</v>
+        <v>3.255191876535246</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.101666666671518</v>
+        <v>1.10166666675883</v>
       </c>
       <c r="F33" t="n">
-        <v>1.471022062890624</v>
+        <v>1.470180504268591</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6512996298999947</v>
+        <v>0.6516984925272564</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>2.405103754134697</v>
+        <v>2.40319257290659</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8392842127991559</v>
+        <v>0.8385666666666669</v>
       </c>
       <c r="F34" t="n">
-        <v>1.39049831246435</v>
+        <v>1.391812413425985</v>
       </c>
       <c r="G34" t="n">
-        <v>0.473048787564049</v>
+        <v>0.4720523184573653</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>3.702447691698134</v>
+        <v>3.709964300264013</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2118015282692</v>
+        <v>1.213954166666667</v>
       </c>
       <c r="F35" t="n">
-        <v>1.506550305542125</v>
+        <v>1.508006548808725</v>
       </c>
       <c r="G35" t="n">
-        <v>0.65746591946508</v>
+        <v>0.6568034072014461</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>3.77825568042374</v>
+        <v>3.773836771499153</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.343552638397468</v>
+        <v>1.341908333333334</v>
       </c>
       <c r="F36" t="n">
-        <v>1.744077204612385</v>
+        <v>1.742667787713233</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.05350048724444201</v>
+        <v>-0.05179847378768354</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>4.234453325689397</v>
+        <v>4.232637625803274</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.394447592264979</v>
+        <v>1.393537500000001</v>
       </c>
       <c r="F37" t="n">
-        <v>2.078631078303745</v>
+        <v>2.078639220439661</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4715703279475429</v>
+        <v>0.4715661881512282</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>3.916557367315194</v>
+        <v>3.918753595324405</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.289844953867511</v>
+        <v>1.2905625</v>
       </c>
       <c r="F38" t="n">
-        <v>1.740312725996888</v>
+        <v>1.74067510215146</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5629441997228337</v>
+        <v>0.5627621691175951</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>3.31392717333642</v>
+        <v>3.316689403227377</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9525991205341778</v>
+        <v>0.9534166666666666</v>
       </c>
       <c r="F39" t="n">
-        <v>1.375366430271601</v>
+        <v>1.377189826542924</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6408456493694793</v>
+        <v>0.6398927181441731</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>2.794622760986553</v>
+        <v>2.783335956812409</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.008325230662447</v>
+        <v>1.004737500000002</v>
       </c>
       <c r="F40" t="n">
-        <v>1.501648373786882</v>
+        <v>1.49901186994967</v>
       </c>
       <c r="G40" t="n">
-        <v>0.902425068352012</v>
+        <v>0.902767399950132</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>4.676564908282197</v>
+        <v>4.676889739221839</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1491,10 +1491,10 @@
         <v>1.680820833333333</v>
       </c>
       <c r="F41" t="n">
-        <v>2.095102849633493</v>
+        <v>2.095595215465843</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3984967167607012</v>
+        <v>0.3982139674296092</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>5.90770933349893</v>
+        <v>5.912445507828182</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2.091606574401687</v>
+        <v>2.093041666666665</v>
       </c>
       <c r="F42" t="n">
-        <v>2.648459388521612</v>
+        <v>2.649208223381719</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4238707389573303</v>
+        <v>0.4235448992122437</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>3.651374334610243</v>
+        <v>3.647221947896016</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.213555925598312</v>
+        <v>1.212120833333334</v>
       </c>
       <c r="F43" t="n">
-        <v>1.439609533097827</v>
+        <v>1.437765745726102</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7747788419048616</v>
+        <v>0.775355378798301</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>3.139081591919745</v>
+        <v>3.135642237892036</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.211105925598313</v>
+        <v>1.209670833333335</v>
       </c>
       <c r="F44" t="n">
-        <v>1.712542276236207</v>
+        <v>1.712531544356678</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2352686431624492</v>
+        <v>0.2352782277189212</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>2.436342300932233</v>
+        <v>2.438453051909731</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8827657872008432</v>
+        <v>0.8834833333333322</v>
       </c>
       <c r="F45" t="n">
-        <v>1.121019089794848</v>
+        <v>1.122315749169248</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4822462346382566</v>
+        <v>0.4810477919925892</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>2.395502886152301</v>
+        <v>2.395960960577379</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1621,10 +1621,10 @@
         <v>0.8292000000000002</v>
       </c>
       <c r="F46" t="n">
-        <v>1.004740253222594</v>
+        <v>1.005283894396668</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5965535207653549</v>
+        <v>0.5961168119660175</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>2.557070992149654</v>
+        <v>2.559383565313087</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8538791666666663</v>
+        <v>0.8545374999999994</v>
       </c>
       <c r="F47" t="n">
-        <v>1.115610843150292</v>
+        <v>1.115057749812388</v>
       </c>
       <c r="G47" t="n">
-        <v>0.124860220270576</v>
+        <v>0.1257277521677481</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>1.39263911955313</v>
+        <v>1.39282959299177</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1673,10 +1673,10 @@
         <v>0.4625958333333342</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5713209573105692</v>
+        <v>0.5714494090322735</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09902552443099599</v>
+        <v>0.09862034156044264</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>3.531642475504349</v>
+        <v>3.529967522917887</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.173192546132489</v>
+        <v>1.172475</v>
       </c>
       <c r="F49" t="n">
-        <v>1.724450040146141</v>
+        <v>1.724855456987628</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1803293034632372</v>
+        <v>0.179943850292868</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>2.775416593756761</v>
+        <v>2.775869784634585</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9278791666666647</v>
+        <v>0.9278791666666648</v>
       </c>
       <c r="F50" t="n">
-        <v>1.198286599871723</v>
+        <v>1.197896703080026</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3057902171861291</v>
+        <v>0.3062419056753027</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>3.192111725800654</v>
+        <v>3.200997935384229</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.057250648803376</v>
+        <v>1.060120833333332</v>
       </c>
       <c r="F51" t="n">
-        <v>1.35977213071795</v>
+        <v>1.360321396919369</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4378650525796679</v>
+        <v>0.4374108234027836</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>2.345169468228907</v>
+        <v>2.345657073596947</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7825708333333341</v>
+        <v>0.7825708333333345</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9845447591433637</v>
+        <v>0.9841123972477269</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1469959182103281</v>
+        <v>0.1477449455711678</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>1.35246948695053</v>
+        <v>1.351733812363661</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4512550461324887</v>
+        <v>0.4509458333333323</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5388343245626034</v>
+        <v>0.5383295029533482</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1165674538807611</v>
+        <v>-0.1144762606896028</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>7.099235259155917</v>
+        <v>7.100440944774822</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1829,10 +1829,10 @@
         <v>2.195354166666667</v>
       </c>
       <c r="F54" t="n">
-        <v>3.453976720785866</v>
+        <v>3.454101238081575</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.4320263922323924</v>
+        <v>-0.432129644386227</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>6.52073916871097</v>
+        <v>6.524160562875887</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2.07248245386751</v>
+        <v>2.07320000000485</v>
       </c>
       <c r="F55" t="n">
-        <v>3.0693820877294</v>
+        <v>3.069849260969532</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2347987367644477</v>
+        <v>-0.2351746487955639</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>2.974202299672775</v>
+        <v>2.982142624048022</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9241265283565108</v>
+        <v>0.926279165638331</v>
       </c>
       <c r="F56" t="n">
-        <v>1.830055977178136</v>
+        <v>1.829505434495295</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2621504655034882</v>
+        <v>0.2625943388771114</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>1.580767026197055</v>
+        <v>1.599507264975328</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5000596307354499</v>
+        <v>0.5057999319067367</v>
       </c>
       <c r="F57" t="n">
-        <v>0.983960209376434</v>
+        <v>0.9832691868463009</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4624860686269564</v>
+        <v>0.4632407816866319</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>4.415433576862746</v>
+        <v>4.420406330235558</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.414139907797171</v>
+        <v>1.415575024233789</v>
       </c>
       <c r="F58" t="n">
-        <v>1.890283042894455</v>
+        <v>1.890673965974767</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.05877831310532589</v>
+        <v>-0.05921628315410388</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>6.428522346212982</v>
+        <v>6.429582655209661</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.929016666680005</v>
+        <v>1.929016671260221</v>
       </c>
       <c r="F59" t="n">
-        <v>2.618327199872682</v>
+        <v>2.618486208666006</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3790288330760025</v>
+        <v>-0.379196332668102</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>7.996076784069913</v>
+        <v>7.996767515859393</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>2.590762500170378</v>
+        <v>2.59076250501556</v>
       </c>
       <c r="F60" t="n">
-        <v>3.517706068796058</v>
+        <v>3.517621801687774</v>
       </c>
       <c r="G60" t="n">
-        <v>0.07968073847601109</v>
+        <v>0.07972483068409075</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>4.328564500593305</v>
+        <v>4.333598708517238</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.431402407791714</v>
+        <v>1.432837501251464</v>
       </c>
       <c r="F61" t="n">
-        <v>1.693345156404559</v>
+        <v>1.693886145036588</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.03927138814237829</v>
+        <v>-0.0399355454944692</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>5.624260779438211</v>
+        <v>5.619888537114946</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.637393427577979</v>
+        <v>1.635958303118707</v>
       </c>
       <c r="F62" t="n">
-        <v>2.322022594942883</v>
+        <v>2.322054209722993</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.1912912452957156</v>
+        <v>-0.1913236848311786</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>5.471054844765166</v>
+        <v>5.474296283955601</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.560028298033835</v>
+        <v>1.560745729665489</v>
       </c>
       <c r="F63" t="n">
-        <v>1.92936092449616</v>
+        <v>1.929614320047551</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.3393479330247278</v>
+        <v>-0.3396997667231239</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>4.667901688117087</v>
+        <v>4.661716101421541</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.522665138398075</v>
+        <v>1.520512500198878</v>
       </c>
       <c r="F64" t="n">
-        <v>2.091924797260526</v>
+        <v>2.091063906812253</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1618314184893311</v>
+        <v>0.1625211400821692</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>5.85029333447323</v>
+        <v>5.855508657107944</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.961344074402295</v>
+        <v>1.962779166773381</v>
       </c>
       <c r="F65" t="n">
-        <v>2.699890009316996</v>
+        <v>2.698975660036459</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6311104049615066</v>
+        <v>0.6313602201913067</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>3.628478991881642</v>
+        <v>3.630340241521001</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.19611995386751</v>
+        <v>1.196837499999999</v>
       </c>
       <c r="F66" t="n">
-        <v>1.522892209195367</v>
+        <v>1.524139641595654</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8104605072980443</v>
+        <v>0.810149868713907</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>3.857595466964291</v>
+        <v>3.858081573543112</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2167,10 +2167,10 @@
         <v>1.185475</v>
       </c>
       <c r="F67" t="n">
-        <v>1.513219690075208</v>
+        <v>1.513613324685888</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.1209636854138803</v>
+        <v>-0.1215469549788968</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>2.9613208787513</v>
+        <v>2.968490939343401</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9663181949358656</v>
+        <v>0.9684708333333325</v>
       </c>
       <c r="F68" t="n">
-        <v>1.40623169950636</v>
+        <v>1.406570873762379</v>
       </c>
       <c r="G68" t="n">
-        <v>0.03802020311079402</v>
+        <v>0.0375561001749446</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>4.166244356171201</v>
+        <v>4.164670295315887</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.286425879449453</v>
+        <v>1.28570833283372</v>
       </c>
       <c r="F69" t="n">
-        <v>1.611768992279194</v>
+        <v>1.612040107206652</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.01080686130891162</v>
+        <v>-0.01114694463185484</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>1.780632398383722</v>
+        <v>1.776296347314234</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5599725933785029</v>
+        <v>0.5585375244860223</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8103421172857298</v>
+        <v>0.8100315918846003</v>
       </c>
       <c r="G70" t="n">
-        <v>0.050142352689587</v>
+        <v>0.05087018950535527</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>2.302027305280542</v>
+        <v>2.308954824980765</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7477015282967859</v>
+        <v>0.7498541745052963</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9944268795879962</v>
+        <v>0.9947003243293968</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2114026171772344</v>
+        <v>0.2109688649133231</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>2.076474429198898</v>
+        <v>2.065738477093236</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.6798293973291129</v>
+        <v>0.6762416677435095</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9457227510730857</v>
+        <v>0.9446886001673277</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2841273596823353</v>
+        <v>0.2856921218014706</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>2.626264503426587</v>
+        <v>2.628799017485774</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8688991205244762</v>
+        <v>0.8696166667054714</v>
       </c>
       <c r="F73" t="n">
-        <v>1.302197061105296</v>
+        <v>1.302432734791215</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002944750866125556</v>
+        <v>0.002583820932945069</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>14.22788190775763</v>
+        <v>14.22615095967762</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.224085092395338</v>
+        <v>2.222650001343626</v>
       </c>
       <c r="F74" t="n">
-        <v>5.19901356474566</v>
+        <v>5.199594266655153</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2555370652340977</v>
+        <v>0.2553707509185864</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.7406648024449805</v>
+        <v>0.7436637357803227</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1864324538675111</v>
+        <v>0.1871500000000004</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2339191277623216</v>
+        <v>0.2332043417263076</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4977049723439729</v>
+        <v>0.5007700053437152</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>0.5179156393060942</v>
+        <v>0.5197763562670501</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.130141666666667</v>
+        <v>0.1305916666666667</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1677783558441686</v>
+        <v>0.1686572214087887</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3268104233324725</v>
+        <v>0.3197392761301304</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.4625027721118953</v>
+        <v>0.460679973370377</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1163758794658224</v>
+        <v>0.1158999999999996</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1783687156527729</v>
+        <v>0.178134983930725</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2255430918621275</v>
+        <v>0.2275714357490682</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>1.293690670755337</v>
+        <v>1.298600938486972</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.318682453867511</v>
+        <v>0.3198499999999997</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5823776962673325</v>
+        <v>0.5825391238649408</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.541867085948879</v>
+        <v>-0.5427219758151458</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>5.038635125002309</v>
+        <v>5.027209282154139</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9981701845299563</v>
+        <v>0.9952999999999997</v>
       </c>
       <c r="F79" t="n">
-        <v>2.25699103997295</v>
+        <v>2.257042776880108</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3649951588402603</v>
+        <v>0.3649660461300407</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.6653712409789873</v>
+        <v>0.6654844709976122</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1686333333333336</v>
+        <v>0.1686333333333333</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2400823069582366</v>
+        <v>0.2393334633240123</v>
       </c>
       <c r="G80" t="n">
-        <v>0.104794551595633</v>
+        <v>0.1103703346006951</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>0.980179813245452</v>
+        <v>0.9831929533417256</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2467449538675102</v>
+        <v>0.2474624999999993</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2784618222514915</v>
+        <v>0.2794120441510464</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.3736986906838231</v>
+        <v>-0.3830898934016667</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>0.8689283268302326</v>
+        <v>0.8690948751225785</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2195125000000004</v>
+        <v>0.2195125000000007</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2798929869563454</v>
+        <v>0.2796906080832899</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.6132800873247113</v>
+        <v>-0.6109479405098881</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>0.5910237067716767</v>
+        <v>0.5955419864294187</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1495725364882778</v>
+        <v>0.1506956521739134</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1814943268922975</v>
+        <v>0.1819668555582015</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.264738316543496</v>
+        <v>-0.2713324960051222</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/validation_daily_metrics/agus7_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus7_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1207572613247764</v>
+        <v>0.3523238173663801</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04369999999999408</v>
+        <v>0.1274999999999977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04369999999999408</v>
+        <v>0.1274999999999977</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>8.371061703095558</v>
+        <v>8.332405809512155</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.802354166666666</v>
+        <v>2.78619850053357</v>
       </c>
       <c r="F3" t="n">
-        <v>4.143963666135358</v>
+        <v>4.153346158890841</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4735754673517265</v>
+        <v>0.4711889764262323</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>4.836187301486302</v>
+        <v>4.818989128841658</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1.695245833333334</v>
+        <v>1.691173500669387</v>
       </c>
       <c r="F4" t="n">
-        <v>3.752317210682399</v>
+        <v>3.728841475369947</v>
       </c>
       <c r="G4" t="n">
-        <v>0.478598353596094</v>
+        <v>0.4851020667519321</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>3.552165285163458</v>
+        <v>3.472039360537298</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.342925</v>
+        <v>1.310952666133096</v>
       </c>
       <c r="F5" t="n">
-        <v>1.704690086447778</v>
+        <v>1.670340369713216</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8064011399514824</v>
+        <v>0.8141246155880653</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>4.257370549256783</v>
+        <v>4.1898593360646</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.642474999999999</v>
+        <v>1.616913999466428</v>
       </c>
       <c r="F6" t="n">
-        <v>1.969613594930063</v>
+        <v>1.943939946602308</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01491582300725858</v>
+        <v>0.01137031748552275</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>2.872184556420647</v>
+        <v>2.884615199967984</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1615625</v>
+        <v>1.166593167336055</v>
       </c>
       <c r="F7" t="n">
-        <v>1.692755898798366</v>
+        <v>1.719658062228107</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4815499293238886</v>
+        <v>0.4649400230030823</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>4.811986362172668</v>
+        <v>4.907119405823508</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.373749999999998</v>
+        <v>1.408552666133096</v>
       </c>
       <c r="F8" t="n">
-        <v>3.382874077214766</v>
+        <v>3.400089189973716</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5363207755812733</v>
+        <v>0.531589531973879</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>6.373306133239377</v>
+        <v>6.313917505655041</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.366791666666666</v>
+        <v>2.340705667200237</v>
       </c>
       <c r="F9" t="n">
-        <v>4.347787197145999</v>
+        <v>4.358624756021141</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2503160394751272</v>
+        <v>0.2465739657227859</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>3.475864490707604</v>
+        <v>3.495355529209259</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.391091666666667</v>
+        <v>1.398602667200237</v>
       </c>
       <c r="F10" t="n">
-        <v>1.685186773278658</v>
+        <v>1.702893938238017</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4373193260828969</v>
+        <v>-0.4676833945738301</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>1.889550496156966</v>
+        <v>1.919490025653045</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7304416666666654</v>
+        <v>0.7415609994664282</v>
       </c>
       <c r="F11" t="n">
-        <v>1.130770086692397</v>
+        <v>1.149653162255946</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6220112999474778</v>
+        <v>0.6092815935951355</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>4.456592836555367</v>
+        <v>4.474893598236949</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.707887500000001</v>
+        <v>1.716015166133099</v>
       </c>
       <c r="F12" t="n">
-        <v>2.168808444457464</v>
+        <v>2.180715000164862</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3173236615271402</v>
+        <v>0.3098074276760548</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>2.326049509136324</v>
+        <v>2.266716966760332</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9471041666666657</v>
+        <v>0.9229568326639436</v>
       </c>
       <c r="F13" t="n">
-        <v>1.15621579643104</v>
+        <v>1.144409992917226</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08334002836332033</v>
+        <v>0.1019639872770589</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>5.250331574655192</v>
+        <v>5.285337101704296</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.901912500000001</v>
+        <v>1.915126499466431</v>
       </c>
       <c r="F14" t="n">
-        <v>2.643826298268604</v>
+        <v>2.639357892099162</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3680827069088464</v>
+        <v>0.3702169446657753</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>4.694954507823409</v>
+        <v>4.665901726904842</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.838116666666667</v>
+        <v>1.827360999466429</v>
       </c>
       <c r="F15" t="n">
-        <v>2.440407160231328</v>
+        <v>2.440167945171671</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2139661035374</v>
+        <v>0.2141201941603484</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>9.660550471814894</v>
+        <v>9.565568332935765</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3.070470833333333</v>
+        <v>3.034184832799762</v>
       </c>
       <c r="F16" t="n">
-        <v>4.679753327589321</v>
+        <v>4.645096596551313</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4745720831531123</v>
+        <v>0.482325563084551</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>2.103130130865802</v>
+        <v>2.073694628973051</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8662041666666657</v>
+        <v>0.8541068326639438</v>
       </c>
       <c r="F17" t="n">
-        <v>1.353071005928119</v>
+        <v>1.340296650464487</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5601535123862541</v>
+        <v>0.5684194969470188</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>3.56807724525173</v>
+        <v>3.532087983763269</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.407020833333332</v>
+        <v>1.390731834002721</v>
       </c>
       <c r="F18" t="n">
-        <v>1.813717415627362</v>
+        <v>1.820504914982502</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1327370751454201</v>
+        <v>0.1262337895244384</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>3.634615217134221</v>
+        <v>3.541279555462892</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.277229166666667</v>
+        <v>1.242051500669388</v>
       </c>
       <c r="F19" t="n">
-        <v>2.324063000347308</v>
+        <v>2.286549513810286</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3547952467608811</v>
+        <v>0.3754560793781495</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>5.503993974654811</v>
+        <v>5.407393031642405</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.912220833333333</v>
+        <v>1.879426499466427</v>
       </c>
       <c r="F20" t="n">
-        <v>2.363775275821145</v>
+        <v>2.317456362917485</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07128609339824576</v>
+        <v>0.1073263659641847</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>4.379212350479129</v>
+        <v>4.278922461127338</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.566716666666667</v>
+        <v>1.531344333866904</v>
       </c>
       <c r="F21" t="n">
-        <v>1.932379545405095</v>
+        <v>1.902711802311039</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6766243005214039</v>
+        <v>0.6864776239868448</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>4.476351758575616</v>
+        <v>4.363261801833445</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.609737500000002</v>
+        <v>1.571515167200239</v>
       </c>
       <c r="F22" t="n">
-        <v>2.24547884991524</v>
+        <v>2.202746315673339</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8137251456316139</v>
+        <v>0.8207474832731697</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>10.74083882593703</v>
+        <v>10.73490489252779</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>3.588416666666668</v>
+        <v>3.587244332663947</v>
       </c>
       <c r="F23" t="n">
-        <v>5.238760624979284</v>
+        <v>5.24563303528272</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.03752037936965325</v>
+        <v>-0.04024428417698234</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>3.495126510781912</v>
+        <v>3.477227658527832</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.259295833333334</v>
+        <v>1.253051500669386</v>
       </c>
       <c r="F24" t="n">
-        <v>1.777967324760686</v>
+        <v>1.773249803855042</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7779642718555515</v>
+        <v>0.7791409735333652</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>4.091701733662049</v>
+        <v>4.049220647662524</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4059625</v>
+        <v>1.391659833866904</v>
       </c>
       <c r="F25" t="n">
-        <v>2.044268245505793</v>
+        <v>2.007818795467189</v>
       </c>
       <c r="G25" t="n">
-        <v>0.521720295912518</v>
+        <v>0.5386237684455308</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>3.705588242921249</v>
+        <v>3.679822639999893</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.177466666666666</v>
+        <v>1.167080667336052</v>
       </c>
       <c r="F26" t="n">
-        <v>1.651794116508873</v>
+        <v>1.65741689487823</v>
       </c>
       <c r="G26" t="n">
-        <v>0.576800959884312</v>
+        <v>0.5739148805143008</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>2.089687992527154</v>
+        <v>1.995523000854955</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6522833333333314</v>
+        <v>0.6223443327997601</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8798919128696041</v>
+        <v>0.854163736439879</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.696873063886372</v>
+        <v>-1.5414648785252</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>3.903433095380862</v>
+        <v>3.93582829894096</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2201375</v>
+        <v>1.231468166133097</v>
       </c>
       <c r="F28" t="n">
-        <v>1.708874525699103</v>
+        <v>1.723573638129149</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2651023386650432</v>
+        <v>0.2524053242443827</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>6.017839927674535</v>
+        <v>6.011095851583931</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.619983333333334</v>
+        <v>1.619680667200236</v>
       </c>
       <c r="F29" t="n">
-        <v>3.0354598332323</v>
+        <v>3.016651181866203</v>
       </c>
       <c r="G29" t="n">
-        <v>0.413311301155306</v>
+        <v>0.4205593862603275</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>4.755576891173575</v>
+        <v>4.838777925917674</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.472556833367287</v>
+        <v>1.496987499466431</v>
       </c>
       <c r="F30" t="n">
-        <v>1.836866873308329</v>
+        <v>1.864371553938313</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.09685559601581861</v>
+        <v>-0.129949481539229</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.4660264521304893</v>
+        <v>0.4813310681516118</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1565640021342833</v>
+        <v>0.1602756673360558</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1565640021342834</v>
+        <v>0.1849189190246694</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9812698735272054</v>
+        <v>0.9738711934646196</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>1.899998752093389</v>
+        <v>1.879974969497855</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6613874999999991</v>
+        <v>0.6549235006693882</v>
       </c>
       <c r="F32" t="n">
-        <v>0.806997621072495</v>
+        <v>0.8023056091797991</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3964765277851815</v>
+        <v>0.4034740879889867</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>3.255191876535246</v>
+        <v>3.197555767327117</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.10166666675883</v>
+        <v>1.080702665997279</v>
       </c>
       <c r="F33" t="n">
-        <v>1.470180504268591</v>
+        <v>1.448749669711098</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6516984925272564</v>
+        <v>0.6617788706936254</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>2.40319257290659</v>
+        <v>2.3922115931957</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8385666666666669</v>
+        <v>0.833327667336055</v>
       </c>
       <c r="F34" t="n">
-        <v>1.391812413425985</v>
+        <v>1.405454866005715</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4720523184573653</v>
+        <v>0.4616517783288439</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>3.709964300264013</v>
+        <v>3.6536959607407</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.213954166666667</v>
+        <v>1.193151499330612</v>
       </c>
       <c r="F35" t="n">
-        <v>1.508006548808725</v>
+        <v>1.48635135213279</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6568034072014461</v>
+        <v>0.6665893427951904</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>3.773836771499153</v>
+        <v>3.835476815758981</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.341908333333334</v>
+        <v>1.362855667336055</v>
       </c>
       <c r="F36" t="n">
-        <v>1.742667787713233</v>
+        <v>1.771933249617638</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.05179847378768354</v>
+        <v>-0.08742182274314292</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>4.232637625803274</v>
+        <v>4.098606434945981</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.393537500000001</v>
+        <v>1.349384833866903</v>
       </c>
       <c r="F37" t="n">
-        <v>2.078639220439661</v>
+        <v>2.036688047340238</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4715661881512282</v>
+        <v>0.4926806905433062</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>3.918753595324405</v>
+        <v>3.852115529179725</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2905625</v>
+        <v>1.264351499330612</v>
       </c>
       <c r="F38" t="n">
-        <v>1.74067510215146</v>
+        <v>1.753393231219278</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5627621691175951</v>
+        <v>0.5563495282484223</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>3.316689403227377</v>
+        <v>3.244906412931206</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9534166666666666</v>
+        <v>0.9295526673360553</v>
       </c>
       <c r="F39" t="n">
-        <v>1.377189826542924</v>
+        <v>1.333315114663854</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6398927181441731</v>
+        <v>0.6624719296942256</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>2.783335956812409</v>
+        <v>2.866398640491217</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.004737500000002</v>
+        <v>1.033381834002724</v>
       </c>
       <c r="F40" t="n">
-        <v>1.49901186994967</v>
+        <v>1.534965095495135</v>
       </c>
       <c r="G40" t="n">
-        <v>0.902767399950132</v>
+        <v>0.898047292404751</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>4.676889739221839</v>
+        <v>4.607689160235878</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.680820833333333</v>
+        <v>1.657365166133096</v>
       </c>
       <c r="F41" t="n">
-        <v>2.095595215465843</v>
+        <v>2.10281534172735</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3982139674296092</v>
+        <v>0.394060058174275</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>5.912445507828182</v>
+        <v>5.909890721327534</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2.093041666666665</v>
+        <v>2.09088899933061</v>
       </c>
       <c r="F42" t="n">
-        <v>2.649208223381719</v>
+        <v>2.655807579606281</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4235448992122437</v>
+        <v>0.4206693450570151</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>3.647221947896016</v>
+        <v>3.667787837211476</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.212120833333334</v>
+        <v>1.218240165997279</v>
       </c>
       <c r="F43" t="n">
-        <v>1.437765745726102</v>
+        <v>1.441653100862342</v>
       </c>
       <c r="G43" t="n">
-        <v>0.775355378798301</v>
+        <v>0.7741389720506098</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>3.135642237892036</v>
+        <v>3.154111702287735</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.209670833333335</v>
+        <v>1.21929316599728</v>
       </c>
       <c r="F44" t="n">
-        <v>1.712531544356678</v>
+        <v>1.74273855643466</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2352782277189212</v>
+        <v>0.2080627434308436</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>2.438453051909731</v>
+        <v>2.330125758694794</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8834833333333322</v>
+        <v>0.8428223338669018</v>
       </c>
       <c r="F45" t="n">
-        <v>1.122315749169248</v>
+        <v>1.093175961266288</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4810477919925892</v>
+        <v>0.5076460849615836</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>2.395960960577379</v>
+        <v>2.394723828907831</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8292000000000002</v>
+        <v>0.8294556659972782</v>
       </c>
       <c r="F46" t="n">
-        <v>1.005283894396668</v>
+        <v>1.018912480813804</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5961168119660175</v>
+        <v>0.585091731159908</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>2.559383565313087</v>
+        <v>2.546832098224709</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8545374999999994</v>
+        <v>0.8508098340027214</v>
       </c>
       <c r="F47" t="n">
-        <v>1.115057749812388</v>
+        <v>1.117752950554799</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1257277521677481</v>
+        <v>0.1214962458445451</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>1.39282959299177</v>
+        <v>1.398858081698232</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4625958333333342</v>
+        <v>0.4638651659972786</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5714494090322735</v>
+        <v>0.5655263152198111</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09862034156044264</v>
+        <v>0.1172091683439966</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>3.529967522917887</v>
+        <v>3.565576721030708</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.172475</v>
+        <v>1.184111000669389</v>
       </c>
       <c r="F49" t="n">
-        <v>1.724855456987628</v>
+        <v>1.709666257323361</v>
       </c>
       <c r="G49" t="n">
-        <v>0.179943850292868</v>
+        <v>0.1943232028910452</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>2.775869784634585</v>
+        <v>2.826016681388846</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9278791666666648</v>
+        <v>0.9445568338669007</v>
       </c>
       <c r="F50" t="n">
-        <v>1.197896703080026</v>
+        <v>1.220725404958306</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3062419056753027</v>
+        <v>0.2795476043197807</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>3.200997935384229</v>
+        <v>3.167805048818394</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.060120833333332</v>
+        <v>1.048015167336055</v>
       </c>
       <c r="F51" t="n">
-        <v>1.360321396919369</v>
+        <v>1.358001128319298</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4374108234027836</v>
+        <v>0.4393283772172656</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>2.345657073596947</v>
+        <v>2.272879696207276</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7825708333333345</v>
+        <v>0.758109833866904</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9841123972477269</v>
+        <v>0.9444661361615643</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1477449455711678</v>
+        <v>0.2150301761425993</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>1.351733812363661</v>
+        <v>1.301411832285462</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4509458333333323</v>
+        <v>0.4341235006693873</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5383295029533482</v>
+        <v>0.5303292341624143</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1144762606896028</v>
+        <v>-0.08159730024013512</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>7.100440944774822</v>
+        <v>6.966582913574502</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2.195354166666667</v>
+        <v>2.15062650053357</v>
       </c>
       <c r="F54" t="n">
-        <v>3.454101238081575</v>
+        <v>3.414584701714469</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.432129644386227</v>
+        <v>-0.3995486195663638</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>6.524160562875887</v>
+        <v>6.431741009208293</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2.07320000000485</v>
+        <v>2.042530666137946</v>
       </c>
       <c r="F55" t="n">
-        <v>3.069849260969532</v>
+        <v>3.064537946537842</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2351746487955639</v>
+        <v>-0.2309042595184361</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>2.982142624048022</v>
+        <v>2.926672084613018</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.926279165638331</v>
+        <v>0.908609833643775</v>
       </c>
       <c r="F56" t="n">
-        <v>1.829505434495295</v>
+        <v>1.798213839469158</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2625943388771114</v>
+        <v>0.2876035753517469</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>1.599507264975328</v>
+        <v>1.683658857943702</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5057999319067367</v>
+        <v>0.5314693341336906</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9832691868463009</v>
+        <v>0.9737900136857143</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4632407816866319</v>
+        <v>0.4735401140288497</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>4.420406330235558</v>
+        <v>4.338190212346622</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.415575024233789</v>
+        <v>1.389605664619698</v>
       </c>
       <c r="F58" t="n">
-        <v>1.890673965974767</v>
+        <v>1.874587227885775</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.05921628315410388</v>
+        <v>-0.04126834932957379</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>6.429582655209661</v>
+        <v>6.411196363053223</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.929016671260221</v>
+        <v>1.924205665943922</v>
       </c>
       <c r="F59" t="n">
-        <v>2.618486208666006</v>
+        <v>2.598232673521141</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.379196332668102</v>
+        <v>-0.3579431593419007</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>7.996767515859393</v>
+        <v>7.965561585933982</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>2.59076250501556</v>
+        <v>2.579559832591184</v>
       </c>
       <c r="F60" t="n">
-        <v>3.517621801687774</v>
+        <v>3.506443103044281</v>
       </c>
       <c r="G60" t="n">
-        <v>0.07972483068409075</v>
+        <v>0.08556464690416787</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>4.333598708517238</v>
+        <v>4.308410472712617</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.432837501251464</v>
+        <v>1.422968167200237</v>
       </c>
       <c r="F61" t="n">
-        <v>1.693886145036588</v>
+        <v>1.702114537712913</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0399355454944692</v>
+        <v>-0.05006347731693794</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>5.619888537114946</v>
+        <v>5.582058728597799</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.635958303118707</v>
+        <v>1.624785968897707</v>
       </c>
       <c r="F62" t="n">
-        <v>2.322054209722993</v>
+        <v>2.325597984296034</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.1913236848311786</v>
+        <v>-0.1949627076203522</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>5.474296283955601</v>
+        <v>5.355644225829473</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.560745729665489</v>
+        <v>1.526273479122851</v>
       </c>
       <c r="F63" t="n">
-        <v>1.929614320047551</v>
+        <v>1.902286368286926</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.3396997667231239</v>
+        <v>-0.3020217718980573</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>4.661716101421541</v>
+        <v>4.60530292254062</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.520512500198878</v>
+        <v>1.502281833997873</v>
       </c>
       <c r="F64" t="n">
-        <v>2.091063906812253</v>
+        <v>2.059493313861775</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1625211400821692</v>
+        <v>0.1876185200441419</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>5.855508657107944</v>
+        <v>5.845441693726274</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.962779166773381</v>
+        <v>1.957523500659687</v>
       </c>
       <c r="F65" t="n">
-        <v>2.698975660036459</v>
+        <v>2.676831415920305</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6313602201913067</v>
+        <v>0.637384550793805</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>3.630340241521001</v>
+        <v>3.61206811631442</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.196837499999999</v>
+        <v>1.185076499466429</v>
       </c>
       <c r="F66" t="n">
-        <v>1.524139641595654</v>
+        <v>1.536484020874353</v>
       </c>
       <c r="G66" t="n">
-        <v>0.810149868713907</v>
+        <v>0.8070621297900529</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>3.858081573543112</v>
+        <v>3.780770144525246</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.185475</v>
+        <v>1.160738999330611</v>
       </c>
       <c r="F67" t="n">
-        <v>1.513613324685888</v>
+        <v>1.495011482834516</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.1215469549788968</v>
+        <v>-0.09414941584260594</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>2.968490939343401</v>
+        <v>2.9489619735679</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9684708333333325</v>
+        <v>0.9610848326639451</v>
       </c>
       <c r="F68" t="n">
-        <v>1.406570873762379</v>
+        <v>1.416457948074978</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0375561001749446</v>
+        <v>0.0239781161158733</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>4.164670295315887</v>
+        <v>4.138208711145127</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.28570833283372</v>
+        <v>1.27602766515812</v>
       </c>
       <c r="F69" t="n">
-        <v>1.612040107206652</v>
+        <v>1.619479445942799</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.01114694463185484</v>
+        <v>-0.02050108129004591</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>1.776296347314234</v>
+        <v>1.816825212810815</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5585375244860223</v>
+        <v>0.5713985025126304</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8100315918846003</v>
+        <v>0.8056912490903322</v>
       </c>
       <c r="G70" t="n">
-        <v>0.05087018950535527</v>
+        <v>0.06101426786429276</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>2.308954824980765</v>
+        <v>2.309792128259299</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7498541745052963</v>
+        <v>0.7499068337359347</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9947003243293968</v>
+        <v>0.9781239343617201</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2109688649133231</v>
+        <v>0.2370476872919473</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>2.065738477093236</v>
+        <v>2.058944362160717</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.6762416677435095</v>
+        <v>0.6738806660942926</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9446886001673277</v>
+        <v>0.9387264257263995</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2856921218014706</v>
+        <v>0.2946800335636107</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>2.628799017485774</v>
+        <v>2.720428877528923</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8696166667054714</v>
+        <v>0.8999890005869284</v>
       </c>
       <c r="F73" t="n">
-        <v>1.302432734791215</v>
+        <v>1.316023329715377</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002583820932945069</v>
+        <v>-0.0183404127675324</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>14.22615095967762</v>
+        <v>14.02730194644615</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.222650001343626</v>
+        <v>2.184989000543271</v>
       </c>
       <c r="F74" t="n">
-        <v>5.199594266655153</v>
+        <v>5.163609395633169</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2553707509185864</v>
+        <v>0.2656418084659424</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.7436637357803227</v>
+        <v>0.6788984129930966</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1871500000000004</v>
+        <v>0.1710860005335711</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2332043417263076</v>
+        <v>0.2342714836460229</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5007700053437152</v>
+        <v>0.4961906036060967</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>0.5197763562670501</v>
+        <v>0.5700604765975076</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1305916666666667</v>
+        <v>0.1432109993306119</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1686572214087887</v>
+        <v>0.1761260919447212</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3197392761301304</v>
+        <v>0.258155447531883</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.460679973370377</v>
+        <v>0.5379507639252147</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1158999999999996</v>
+        <v>0.1353889994664286</v>
       </c>
       <c r="F77" t="n">
-        <v>0.178134983930725</v>
+        <v>0.1935755897528275</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2275714357490682</v>
+        <v>0.08786090611826236</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>1.298600938486972</v>
+        <v>1.25526439873813</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3198499999999997</v>
+        <v>0.3090139993306111</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5825391238649408</v>
+        <v>0.5762220391230678</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.5427219758151458</v>
+        <v>-0.5094446741825447</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>5.027209282154139</v>
+        <v>5.078682433533435</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9952999999999997</v>
+        <v>1.008197332663944</v>
       </c>
       <c r="F79" t="n">
-        <v>2.257042776880108</v>
+        <v>2.284497507495246</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3649660461300407</v>
+        <v>0.3494229431669527</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.6654844709976122</v>
+        <v>0.8531155620065054</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1686333333333333</v>
+        <v>0.2159193338669033</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2393334633240123</v>
+        <v>0.2755412172391735</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1103703346006951</v>
+        <v>-0.1791676359812517</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>0.9831929533417256</v>
+        <v>0.8773724679595072</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2474624999999993</v>
+        <v>0.2207651659972774</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2794120441510464</v>
+        <v>0.2649557977828602</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.3830898934016667</v>
+        <v>-0.2436753228266124</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>0.8690948751225785</v>
+        <v>0.8597208125808652</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2195125000000007</v>
+        <v>0.2170681661330981</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2796906080832899</v>
+        <v>0.2888803701007531</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.6109479405098881</v>
+        <v>-0.7185485403813998</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>0.5955419864294187</v>
+        <v>0.6097132739144995</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1506956521739134</v>
+        <v>0.1542288688667272</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1819668555582015</v>
+        <v>0.1983626200417452</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.2713324960051222</v>
+        <v>-0.5107556915850782</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
